--- a/CC_Sound_List.xlsx
+++ b/CC_Sound_List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\프로젝트CC작업내용\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C540CC1D-9DD2-4CE4-89C5-862F8FD1792A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF288DD5-9DCD-4D42-984B-4CEA434D4F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{5437763E-761A-4F42-872C-FC7D35FC93C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5437763E-761A-4F42-872C-FC7D35FC93C6}"/>
   </bookViews>
   <sheets>
     <sheet name="세팅" sheetId="13" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="213">
   <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -380,10 +380,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>로또</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>로또 사용시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -392,10 +388,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>긴급탈출장치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>방패 착용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -412,23 +404,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>슝~</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>띠리링</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>띠링</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>신속신발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수웅~</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -790,6 +770,133 @@
   </si>
   <si>
     <t>[Item_EmergencyFood.cpp]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AItem_SpeedShoes::UseEffect_Implementation 함수 내 코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeedShoes_Cue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AItem_Shield::UseEffect_Implementation 함수 내 코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freesound_community-pvc-rocket-cannon_2-106658</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freesound_community-heal-up-39285</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liecio-collect-points-190037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큰 피격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin_Cue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player_Character</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freesound_community-teleport-90137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AItem_EmergencyEscape::UseEffect_Implementation 함수 내 코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_EmergencyEscape</t>
+  </si>
+  <si>
+    <t>Teleport_Cue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시전자와 피시전자 둘 다 각자 소리 재생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type2</t>
+  </si>
+  <si>
+    <t>Type3</t>
+  </si>
+  <si>
+    <t>내 몸에서 재생되는 사운드(3D)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 위치에서 재생되는 사운드(3D)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나 혼자 듣는 사운드(2D)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACoin::OnTriggerBeginOverlap 함수 안에서
+PlayerState-&gt;AddCoin(CoinValue); 코드 다음줄에
+Player-&gt;Client_PlaySound2D(Player-&gt;CoinPickupSound); 추가
+AMagnetCoin::Tick함수 안에서
+TargetPlayer-&gt;GetThePlayerState()-&gt;AddCoin(MagnetCoinValue);코드 다음줄에
+	TargetPlayer-&gt;Client_PlaySound2D(TargetPlayer-&gt;CoinPickupSound); 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 습득시
+CoinPickupSound는 Player_Character.h에서 선언하고 블루프린트에 참조설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>freesound_gamestudio-purchase-success-384963</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lotto_Cue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Lotto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AItem_Lotto::UseEffect_Implementation 함수 내 코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당클래스에서 자체적으로 재생함수 실행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1007,6 +1114,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>182657</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>67297</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36A181A5-61CC-04C4-28A3-EF94C90E8065}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9601200" y="2733675"/>
+          <a:ext cx="12050807" cy="4458322"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1162,8 +1313,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>574053</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1278903</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>67649</xdr:rowOff>
     </xdr:to>
@@ -1206,8 +1357,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>574053</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1278903</xdr:colOff>
       <xdr:row>86</xdr:row>
       <xdr:rowOff>1053</xdr:rowOff>
     </xdr:to>
@@ -1250,8 +1401,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>649173</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>553923</xdr:colOff>
       <xdr:row>99</xdr:row>
       <xdr:rowOff>114667</xdr:rowOff>
     </xdr:to>
@@ -1294,8 +1445,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>315661</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>5363911</xdr:colOff>
       <xdr:row>148</xdr:row>
       <xdr:rowOff>20427</xdr:rowOff>
     </xdr:to>
@@ -1343,8 +1494,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>515596</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>96496</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>29135</xdr:rowOff>
     </xdr:to>
@@ -1381,14 +1532,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>391763</xdr:colOff>
+      <xdr:colOff>420338</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>191170</xdr:rowOff>
     </xdr:to>
@@ -1800,21 +1951,21 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="O2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="P2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="O3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
@@ -1822,7 +1973,7 @@
         <v>34</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
@@ -1830,12 +1981,12 @@
         <v>37</v>
       </c>
       <c r="P5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
@@ -1843,17 +1994,52 @@
         <v>38</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="O9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>205</v>
+      </c>
+      <c r="P10" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>166</v>
+        <v>161</v>
+      </c>
+      <c r="O11" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="O12" t="s">
+        <v>199</v>
+      </c>
+      <c r="P12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="O13" t="s">
+        <v>200</v>
+      </c>
+      <c r="P13" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1900,7 +2086,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -1926,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C3"/>
       <c r="D3"/>
@@ -1938,7 +2124,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -2102,7 +2288,7 @@
     </row>
     <row r="29" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +2334,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -2374,7 +2560,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -2473,22 +2659,22 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -2514,7 +2700,7 @@
     <col min="2" max="2" width="21.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="76" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.25" style="1" bestFit="1" customWidth="1"/>
@@ -2542,7 +2728,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -2758,10 +2944,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -2781,13 +2967,19 @@
       <c r="J8" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="L8" s="1" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
       <c r="B9" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -2807,10 +2999,45 @@
       <c r="J9" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="L9" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.3">
@@ -2828,7 +3055,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87EE2B9F-7F07-4138-92A6-2ED6EA3CDE39}">
-  <dimension ref="A2:L23"/>
+  <dimension ref="A2:M23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
@@ -2836,17 +3063,18 @@
     <col min="3" max="3" width="20.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="55.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="43" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="43" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2863,45 +3091,48 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>36</v>
@@ -2909,17 +3140,20 @@
       <c r="I3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.5</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2938,131 +3172,232 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5"/>
-      <c r="E5" s="2"/>
-      <c r="L5" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="D7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F20" s="2"/>
-    </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F23" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G20" s="2"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G23" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3108,7 +3443,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -3134,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C3"/>
       <c r="D3"/>
@@ -3146,7 +3481,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -3158,16 +3493,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5" s="2"/>
       <c r="K5" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -3175,7 +3510,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -3185,7 +3520,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C7"/>
       <c r="D7"/>
@@ -3195,7 +3530,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -3203,7 +3538,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -3212,7 +3547,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -3220,7 +3555,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.3">
@@ -3272,7 +3607,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -3298,10 +3633,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D3"/>
       <c r="E3" s="2"/>
@@ -3312,10 +3647,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D4"/>
       <c r="E4" s="2"/>
@@ -3326,10 +3661,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D5"/>
     </row>
@@ -3338,10 +3673,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D6"/>
     </row>
@@ -3350,10 +3685,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -3361,10 +3696,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -3372,14 +3707,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D9"/>
       <c r="E9" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
@@ -3397,10 +3732,10 @@
         <v>3.3</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -3408,10 +3743,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -3419,47 +3754,47 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -3467,67 +3802,67 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D24" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="D25" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="115.5" x14ac:dyDescent="0.3">
       <c r="D28" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E33" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="5:6" ht="82.5" x14ac:dyDescent="0.3">
       <c r="E34" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3574,7 +3909,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
